--- a/backend/scripts/audit-output/expeditor-smoke/ex-3.0.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-3.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t xml:space="preserve">Водитель: </t>
   </si>
@@ -790,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AQ74"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" style="1" customWidth="1"/>
     <col min="2" max="43" width="12" customWidth="1"/>
@@ -4663,6 +4663,6 @@
     <mergeCell ref="A60:AQ61"/>
   </mergeCells>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>